--- a/artfynd/A 39000-2025 artfynd.xlsx
+++ b/artfynd/A 39000-2025 artfynd.xlsx
@@ -945,12 +945,7 @@
         <v>63225830</v>
       </c>
       <c r="B4" t="n">
-        <v>57508</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Dokumentation efterfrågas</t>
-        </is>
+        <v>56613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566700.154629018</v>
+        <v>566700</v>
       </c>
       <c r="R4" t="n">
-        <v>6306052.745510211</v>
+        <v>6306053</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1039,19 +1034,9 @@
           <t>2012-08-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-08-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 39000-2025 artfynd.xlsx
+++ b/artfynd/A 39000-2025 artfynd.xlsx
@@ -945,7 +945,7 @@
         <v>63225830</v>
       </c>
       <c r="B4" t="n">
-        <v>56613</v>
+        <v>56615</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Eriksson, Amie Ringberg</t>
+          <t>Amie Ringberg, Alexander Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 39000-2025 artfynd.xlsx
+++ b/artfynd/A 39000-2025 artfynd.xlsx
@@ -1061,7 +1061,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amie Ringberg, Alexander Eriksson</t>
+          <t>Alexander Eriksson, Amie Ringberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 39000-2025 artfynd.xlsx
+++ b/artfynd/A 39000-2025 artfynd.xlsx
@@ -945,7 +945,7 @@
         <v>63225830</v>
       </c>
       <c r="B4" t="n">
-        <v>56615</v>
+        <v>56617</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39000-2025 artfynd.xlsx
+++ b/artfynd/A 39000-2025 artfynd.xlsx
@@ -1061,7 +1061,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Eriksson, Amie Ringberg</t>
+          <t>Amie Ringberg, Alexander Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 39000-2025 artfynd.xlsx
+++ b/artfynd/A 39000-2025 artfynd.xlsx
@@ -945,7 +945,7 @@
         <v>63225830</v>
       </c>
       <c r="B4" t="n">
-        <v>56617</v>
+        <v>56620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39000-2025 artfynd.xlsx
+++ b/artfynd/A 39000-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63189454</v>
+        <v>63181458</v>
       </c>
       <c r="B2" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>100015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -739,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566700.154629018</v>
+        <v>566700</v>
       </c>
       <c r="R2" t="n">
-        <v>6306052.745510211</v>
+        <v>6306053</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,24 +767,9 @@
           <t>2012-08-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-08-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>lokal-ID: 50  Box-ID: 57AA</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -816,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63181458</v>
+        <v>63189454</v>
       </c>
       <c r="B3" t="n">
-        <v>56162</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,26 +807,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100015</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -916,6 +891,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-08-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>lokal-ID: 50  Box-ID: 57AA</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,7 +925,7 @@
         <v>63225830</v>
       </c>
       <c r="B4" t="n">
-        <v>56620</v>
+        <v>56840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39000-2025 artfynd.xlsx
+++ b/artfynd/A 39000-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63181458</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63189454</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1045,8 +1060,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63225830</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>